--- a/VT_ELAND_ALL_V02.xlsx
+++ b/VT_ELAND_ALL_V02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_MACIEK\Uczelnia\Przedmioty\Integrated Energy Resource Planning\ELAND_02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/GalaLorenzo/Downloads/ELAND-main 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26E2A42-3B2D-4B2A-91EC-577E4FA2F47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C121F63B-FC07-314C-8F40-EC89262A9DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="10" r:id="rId1"/>
@@ -253,7 +253,7 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -264,7 +264,7 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -273,7 +273,7 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -284,7 +284,7 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -293,7 +293,7 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -304,7 +304,7 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -313,7 +313,7 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -324,7 +324,7 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -333,7 +333,7 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -612,7 +612,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="202">
   <si>
     <t>Define Commodities</t>
   </si>
@@ -1206,6 +1206,18 @@
   </si>
   <si>
     <t>S2W2D2</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>STG_DN_1P</t>
+  </si>
+  <si>
+    <t>ELE_MV</t>
+  </si>
+  <si>
+    <t>Electricity Medium Voltage</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1227,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1366,6 +1378,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1867,7 +1886,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2081,6 +2100,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2200,7 +2221,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2933</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>99645</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1989584" cy="350352"/>
@@ -2411,7 +2432,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>600808</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>87922</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3601692" cy="350352"/>
@@ -3202,21 +3223,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4117804-2E85-47EE-BA5B-568C5E98E06A}">
   <dimension ref="B2:M17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="1.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="1.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="1.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B2" s="9" t="s">
         <v>92</v>
       </c>
@@ -3231,10 +3252,10 @@
       <c r="L2" s="104"/>
       <c r="M2" s="104"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F3" s="9"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>70</v>
       </c>
@@ -3242,7 +3263,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>72</v>
       </c>
@@ -3277,7 +3298,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F6">
         <v>1</v>
       </c>
@@ -3303,7 +3324,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>82</v>
       </c>
@@ -3311,7 +3332,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>84</v>
       </c>
@@ -3343,7 +3364,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>85</v>
       </c>
@@ -3351,7 +3372,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>87</v>
       </c>
@@ -3383,7 +3404,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>93</v>
       </c>
@@ -3406,7 +3427,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>96</v>
       </c>
@@ -3438,7 +3459,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
         <v>100</v>
       </c>
@@ -3454,9 +3475,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA14610B-F5EC-4107-A8FB-0F277B7332F9}">
   <dimension ref="B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" s="9" t="s">
         <v>133</v>
       </c>
@@ -3470,7 +3491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495D73C4-1CB8-4502-8C15-49A7C0384D59}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3479,24 +3500,24 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:L23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:L24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="3.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="3.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="3.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="5.83203125" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" customWidth="1"/>
+    <col min="10" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="11" width="10.5" customWidth="1"/>
+    <col min="12" max="12" width="3.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" ht="18" x14ac:dyDescent="0.2">
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3509,8 +3530,8 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="17"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
@@ -3523,7 +3544,7 @@
       <c r="K4" s="25"/>
       <c r="L4" s="22"/>
     </row>
-    <row r="5" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="18"/>
       <c r="C5" s="90" t="s">
         <v>1</v>
@@ -3538,7 +3559,7 @@
       <c r="K5" s="90"/>
       <c r="L5" s="23"/>
     </row>
-    <row r="6" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18"/>
       <c r="C6" s="55" t="s">
         <v>135</v>
@@ -3569,7 +3590,7 @@
       </c>
       <c r="L6" s="23"/>
     </row>
-    <row r="7" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="18"/>
       <c r="C7" s="92" t="s">
         <v>9</v>
@@ -3600,7 +3621,7 @@
       </c>
       <c r="L7" s="23"/>
     </row>
-    <row r="8" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="18"/>
       <c r="C8" s="68" t="s">
         <v>15</v>
@@ -3623,7 +3644,7 @@
       <c r="K8" s="68"/>
       <c r="L8" s="23"/>
     </row>
-    <row r="9" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="18"/>
       <c r="C9" s="77" t="s">
         <v>15</v>
@@ -3646,7 +3667,7 @@
       <c r="K9" s="77"/>
       <c r="L9" s="23"/>
     </row>
-    <row r="10" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="18"/>
       <c r="C10" s="68" t="s">
         <v>15</v>
@@ -3669,7 +3690,7 @@
       <c r="K10" s="68"/>
       <c r="L10" s="23"/>
     </row>
-    <row r="11" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="18"/>
       <c r="C11" s="77" t="s">
         <v>15</v>
@@ -3694,7 +3715,7 @@
       </c>
       <c r="L11" s="23"/>
     </row>
-    <row r="12" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="18"/>
       <c r="C12" s="68" t="s">
         <v>15</v>
@@ -3717,7 +3738,7 @@
       <c r="K12" s="68"/>
       <c r="L12" s="23"/>
     </row>
-    <row r="13" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="18"/>
       <c r="C13" s="103" t="s">
         <v>138</v>
@@ -3740,89 +3761,112 @@
       <c r="K13" s="103"/>
       <c r="L13" s="23"/>
     </row>
-    <row r="14" spans="2:12" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="19"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="21"/>
-    </row>
-    <row r="17" spans="3:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="105" t="s">
+    <row r="14" spans="2:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="18"/>
+      <c r="C14" s="118" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118" t="s">
+        <v>200</v>
+      </c>
+      <c r="F14" s="118" t="s">
+        <v>201</v>
+      </c>
+      <c r="G14" s="118" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118" t="s">
+        <v>187</v>
+      </c>
+      <c r="J14" s="118"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="23"/>
+    </row>
+    <row r="15" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="21"/>
+    </row>
+    <row r="18" spans="3:5" ht="19" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="105" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="105"/>
-      <c r="E17" s="105"/>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="62" t="s">
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C19" s="62" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="106" t="s">
+      <c r="D19" s="106" t="s">
         <v>141</v>
       </c>
-      <c r="E18" s="107"/>
-    </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C19" s="59" t="s">
+      <c r="E19" s="107"/>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C20" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="110" t="s">
+      <c r="D20" s="110" t="s">
         <v>139</v>
       </c>
-      <c r="E19" s="110"/>
-    </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C20" s="60" t="s">
+      <c r="E20" s="110"/>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C21" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="D20" s="109" t="s">
+      <c r="D21" s="109" t="s">
         <v>142</v>
       </c>
-      <c r="E20" s="109"/>
-    </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C21" s="59" t="s">
+      <c r="E21" s="109"/>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C22" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="110" t="s">
+      <c r="D22" s="110" t="s">
         <v>143</v>
       </c>
-      <c r="E21" s="110"/>
-    </row>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C22" s="60" t="s">
+      <c r="E22" s="110"/>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C23" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="109" t="s">
+      <c r="D23" s="109" t="s">
         <v>146</v>
       </c>
-      <c r="E22" s="109"/>
-    </row>
-    <row r="23" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="61" t="s">
+      <c r="E23" s="109"/>
+    </row>
+    <row r="24" spans="3:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="D23" s="108" t="s">
+      <c r="D24" s="108" t="s">
         <v>147</v>
       </c>
-      <c r="E23" s="108"/>
+      <c r="E24" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D24:E24"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D19:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -3831,28 +3875,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D37998-97B2-47BE-BFC8-510092DE769F}">
-  <dimension ref="B2:L33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:L34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="3.28515625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="3.33203125" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" customWidth="1"/>
-    <col min="12" max="12" width="3.28515625" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="3.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" ht="18" x14ac:dyDescent="0.2">
       <c r="C2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="17"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -3865,7 +3909,7 @@
       <c r="K4" s="26"/>
       <c r="L4" s="22"/>
     </row>
-    <row r="5" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="18"/>
       <c r="C5" s="27" t="s">
         <v>19</v>
@@ -3880,7 +3924,7 @@
       <c r="K5" s="29"/>
       <c r="L5" s="23"/>
     </row>
-    <row r="6" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18"/>
       <c r="C6" s="30" t="s">
         <v>20</v>
@@ -3911,7 +3955,7 @@
       </c>
       <c r="L6" s="23"/>
     </row>
-    <row r="7" spans="2:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="18"/>
       <c r="C7" s="97" t="s">
         <v>29</v>
@@ -3942,383 +3986,411 @@
       </c>
       <c r="L7" s="23"/>
     </row>
-    <row r="8" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="18"/>
-      <c r="C8" s="100" t="s">
+      <c r="C8" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="J8" s="14"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="23"/>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="18"/>
+      <c r="C9" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="101"/>
-      <c r="J8" s="101"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="23"/>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="32" t="s">
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="101"/>
+      <c r="J9" s="101"/>
+      <c r="K9" s="102"/>
+      <c r="L9" s="23"/>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="18"/>
+      <c r="C10" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14" t="s">
+      <c r="D10" s="14"/>
+      <c r="E10" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F10" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G10" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H10" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I10" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="23"/>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="34" t="s">
+      <c r="J10" s="14"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="23"/>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="18"/>
+      <c r="C11" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15" t="s">
+      <c r="D11" s="15"/>
+      <c r="E11" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G11" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H11" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I11" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="23"/>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="18"/>
-      <c r="C11" s="32" t="s">
+      <c r="J11" s="15"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="23"/>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="18"/>
+      <c r="C12" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14" t="s">
+      <c r="D12" s="14"/>
+      <c r="E12" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F12" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G12" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H12" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I12" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="23"/>
-    </row>
-    <row r="12" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="100" t="s">
+      <c r="J12" s="14"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="23"/>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="18"/>
+      <c r="C13" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="101"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="102"/>
-      <c r="L12" s="23"/>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="32" t="s">
+      <c r="D13" s="101"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="101"/>
+      <c r="J13" s="101"/>
+      <c r="K13" s="102"/>
+      <c r="L13" s="23"/>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="18"/>
+      <c r="C14" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14" t="s">
+      <c r="D14" s="14"/>
+      <c r="E14" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F14" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G14" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H14" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I14" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="23"/>
-    </row>
-    <row r="14" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="18"/>
-      <c r="C14" s="34" t="s">
+      <c r="J14" s="14"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="23"/>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="18"/>
+      <c r="C15" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15" t="s">
+      <c r="D15" s="15"/>
+      <c r="E15" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G15" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H15" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I15" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="23"/>
-    </row>
-    <row r="15" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="68" t="s">
+      <c r="J15" s="15"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="23"/>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="18"/>
+      <c r="C16" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68" t="s">
+      <c r="D16" s="68"/>
+      <c r="E16" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="F15" s="68" t="s">
+      <c r="F16" s="68" t="s">
         <v>173</v>
       </c>
-      <c r="G15" s="68" t="s">
+      <c r="G16" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="H15" s="68" t="s">
+      <c r="H16" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="68" t="s">
+      <c r="I16" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="23"/>
-    </row>
-    <row r="16" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="87" t="s">
+      <c r="J16" s="68"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="23"/>
+    </row>
+    <row r="17" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="18"/>
+      <c r="C17" s="87" t="s">
         <v>178</v>
       </c>
-      <c r="D16" s="87"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="87"/>
-      <c r="G16" s="87"/>
-      <c r="H16" s="87"/>
-      <c r="I16" s="87"/>
-      <c r="J16" s="87"/>
-      <c r="K16" s="87"/>
-      <c r="L16" s="23"/>
-    </row>
-    <row r="17" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="18"/>
-      <c r="C17" s="68" t="s">
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="87"/>
+      <c r="I17" s="87"/>
+      <c r="J17" s="87"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="23"/>
+    </row>
+    <row r="18" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="18"/>
+      <c r="C18" s="68" t="s">
         <v>183</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68" t="s">
+      <c r="D18" s="68"/>
+      <c r="E18" s="68" t="s">
         <v>184</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="F18" s="68" t="s">
         <v>185</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="G18" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H18" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="I17" s="68" t="s">
+      <c r="I18" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="23"/>
-    </row>
-    <row r="18" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="18"/>
-      <c r="C18" s="85" t="s">
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="23"/>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="18"/>
+      <c r="C19" s="85" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="85" t="s">
+      <c r="D19" s="85" t="s">
         <v>179</v>
       </c>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="85"/>
-      <c r="J18" s="85"/>
-      <c r="K18" s="85"/>
-      <c r="L18" s="23"/>
-    </row>
-    <row r="19" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="18"/>
-      <c r="C19" s="89" t="s">
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="85"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="85"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="23"/>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="18"/>
+      <c r="C20" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89" t="s">
+      <c r="D20" s="89"/>
+      <c r="E20" s="89" t="s">
         <v>181</v>
       </c>
-      <c r="F19" s="89" t="s">
+      <c r="F20" s="89" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="89" t="s">
+      <c r="G20" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="H19" s="89" t="s">
+      <c r="H20" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="I19" s="89" t="s">
+      <c r="I20" s="89" t="s">
         <v>187</v>
       </c>
-      <c r="J19" s="89"/>
-      <c r="K19" s="89"/>
-      <c r="L19" s="23"/>
-    </row>
-    <row r="20" spans="2:12" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="19"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="21"/>
-    </row>
-    <row r="23" spans="2:12" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="105" t="s">
+      <c r="J20" s="89"/>
+      <c r="K20" s="89"/>
+      <c r="L20" s="23"/>
+    </row>
+    <row r="21" spans="2:12" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="19"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="21"/>
+    </row>
+    <row r="24" spans="2:12" ht="19" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="105" t="s">
         <v>166</v>
       </c>
-      <c r="D23" s="105"/>
-      <c r="E23" s="105"/>
-    </row>
-    <row r="24" spans="2:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="16" t="s">
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+    </row>
+    <row r="25" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="D24" s="112" t="s">
+      <c r="D25" s="112" t="s">
         <v>141</v>
       </c>
-      <c r="E24" s="113"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C25" s="63" t="s">
+      <c r="E25" s="113"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C26" s="63" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="116" t="s">
+      <c r="D26" s="116" t="s">
         <v>164</v>
       </c>
-      <c r="E25" s="116"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C26" s="60" t="s">
+      <c r="E26" s="116"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C27" s="60" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="114" t="s">
+      <c r="D27" s="114" t="s">
         <v>162</v>
       </c>
-      <c r="E26" s="114"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C27" s="59" t="s">
+      <c r="E27" s="114"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C28" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="D27" s="115" t="s">
+      <c r="D28" s="115" t="s">
         <v>160</v>
       </c>
-      <c r="E27" s="115"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C28" s="60" t="s">
+      <c r="E28" s="115"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C29" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="D28" s="114" t="s">
+      <c r="D29" s="114" t="s">
         <v>159</v>
       </c>
-      <c r="E28" s="114"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C29" s="59" t="s">
+      <c r="E29" s="114"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C30" s="59" t="s">
         <v>150</v>
       </c>
-      <c r="D29" s="115" t="s">
+      <c r="D30" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="E29" s="115"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C30" s="60" t="s">
+      <c r="E30" s="115"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C31" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="114" t="s">
+      <c r="D31" s="114" t="s">
         <v>165</v>
       </c>
-      <c r="E30" s="114"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C31" s="59" t="s">
+      <c r="E31" s="114"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C32" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="D31" s="115" t="s">
+      <c r="D32" s="115" t="s">
         <v>161</v>
       </c>
-      <c r="E31" s="115"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C32" s="60" t="s">
+      <c r="E32" s="115"/>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C33" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="D32" s="114" t="s">
+      <c r="D33" s="114" t="s">
         <v>156</v>
       </c>
-      <c r="E32" s="114"/>
-    </row>
-    <row r="33" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="61" t="s">
+      <c r="E33" s="114"/>
+    </row>
+    <row r="34" spans="3:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="D33" s="111" t="s">
+      <c r="D34" s="111" t="s">
         <v>163</v>
       </c>
-      <c r="E33" s="111"/>
+      <c r="E34" s="111"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D25:E25"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="D24:E24"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="D30:E30"/>
@@ -4326,7 +4398,6 @@
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D25:E25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -4335,28 +4406,28 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1952914-7966-4DC5-AB8B-D64E02D1F6E6}">
-  <dimension ref="B2:H12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:H13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="3.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="3.28515625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="3.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="3.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="6"/>
     </row>
-    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="17"/>
       <c r="C4" s="46"/>
       <c r="D4" s="47"/>
@@ -4365,7 +4436,7 @@
       <c r="G4" s="26"/>
       <c r="H4" s="22"/>
     </row>
-    <row r="5" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="18"/>
       <c r="C5" s="39" t="s">
         <v>41</v>
@@ -4376,7 +4447,7 @@
       <c r="G5" s="38"/>
       <c r="H5" s="23"/>
     </row>
-    <row r="6" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18"/>
       <c r="C6" s="40" t="s">
         <v>22</v>
@@ -4395,7 +4466,7 @@
       </c>
       <c r="H6" s="23"/>
     </row>
-    <row r="7" spans="2:8" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="42" x14ac:dyDescent="0.2">
       <c r="B7" s="18"/>
       <c r="C7" s="93" t="s">
         <v>43</v>
@@ -4414,7 +4485,7 @@
       </c>
       <c r="H7" s="23"/>
     </row>
-    <row r="8" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="18"/>
       <c r="C8" s="82" t="s">
         <v>50</v>
@@ -4429,14 +4500,14 @@
       </c>
       <c r="H8" s="23"/>
     </row>
-    <row r="9" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="18"/>
       <c r="C9" s="44" t="str">
-        <f>FI_Process!E9</f>
+        <f>FI_Process!E10</f>
         <v>IMP_OIL</v>
       </c>
       <c r="D9" s="68" t="str">
-        <f>FI_Process!F9</f>
+        <f>FI_Process!F10</f>
         <v>Import of Fuel Oil</v>
       </c>
       <c r="E9" s="68" t="str">
@@ -4449,14 +4520,14 @@
       </c>
       <c r="H9" s="23"/>
     </row>
-    <row r="10" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="18"/>
       <c r="C10" s="64" t="str">
-        <f>FI_Process!E10</f>
+        <f>FI_Process!E11</f>
         <v>MIN_NAT_GAS</v>
       </c>
       <c r="D10" s="77" t="str">
-        <f>FI_Process!F10</f>
+        <f>FI_Process!F11</f>
         <v>Supply Natural Gas</v>
       </c>
       <c r="E10" s="77" t="str">
@@ -4469,14 +4540,14 @@
       </c>
       <c r="H10" s="23"/>
     </row>
-    <row r="11" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="18"/>
       <c r="C11" s="79" t="str">
-        <f>FI_Process!E11</f>
+        <f>FI_Process!E12</f>
         <v>MIN_WIND_ON</v>
       </c>
       <c r="D11" s="80" t="str">
-        <f>FI_Process!F11</f>
+        <f>FI_Process!F12</f>
         <v>Supply Wind Onshore</v>
       </c>
       <c r="E11" s="80" t="str">
@@ -4489,14 +4560,32 @@
       </c>
       <c r="H11" s="23"/>
     </row>
-    <row r="12" spans="2:8" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="21"/>
+    <row r="12" spans="2:8" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="18"/>
+      <c r="C12" s="117" t="str">
+        <f>FI_Process!E8</f>
+        <v>STG_DN_1P</v>
+      </c>
+      <c r="D12" s="117" t="str">
+        <f>FI_Process!F8</f>
+        <v>Storage</v>
+      </c>
+      <c r="E12" s="117" t="str">
+        <f>FI_Comm!E14</f>
+        <v>ELE_MV</v>
+      </c>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="23"/>
+    </row>
+    <row r="13" spans="2:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
@@ -4507,27 +4596,27 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B95FE246-6927-4E10-AB96-C02BF4616A2F}">
-  <dimension ref="B2:P23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:P24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="3.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="3.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.5" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" customWidth="1"/>
+    <col min="10" max="10" width="12.5" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.28515625" customWidth="1"/>
-    <col min="15" max="16" width="17.28515625" customWidth="1"/>
-    <col min="17" max="17" width="11.140625" customWidth="1"/>
+    <col min="13" max="13" width="3.33203125" customWidth="1"/>
+    <col min="15" max="16" width="17.33203125" customWidth="1"/>
+    <col min="17" max="17" width="11.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:16" ht="16" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>116</v>
       </c>
@@ -4535,10 +4624,10 @@
       <c r="E2" s="5"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="17"/>
       <c r="C4" s="46"/>
       <c r="D4" s="47"/>
@@ -4552,7 +4641,7 @@
       <c r="L4" s="26"/>
       <c r="M4" s="22"/>
     </row>
-    <row r="5" spans="2:16" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="18"/>
       <c r="C5" s="39" t="s">
         <v>41</v>
@@ -4568,7 +4657,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="23"/>
     </row>
-    <row r="6" spans="2:16" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18"/>
       <c r="C6" s="40" t="s">
         <v>22</v>
@@ -4605,7 +4694,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" ht="42" x14ac:dyDescent="0.2">
       <c r="B7" s="18"/>
       <c r="C7" s="93" t="s">
         <v>43</v>
@@ -4645,7 +4734,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="18"/>
       <c r="C8" s="86" t="s">
         <v>50</v>
@@ -4679,14 +4768,14 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="18"/>
       <c r="C9" s="44" t="str">
-        <f>FI_Process!E13</f>
+        <f>FI_Process!E14</f>
         <v>EX_PP_OIL</v>
       </c>
       <c r="D9" s="68" t="str">
-        <f>FI_Process!F13</f>
+        <f>FI_Process!F14</f>
         <v>Power Plant - Fuel Oil</v>
       </c>
       <c r="E9" s="68" t="str">
@@ -4725,14 +4814,14 @@
         <v>252.28800000000001</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="18"/>
       <c r="C10" s="64" t="str">
-        <f>FI_Process!E14</f>
+        <f>FI_Process!E15</f>
         <v>EX_PP_NAT_GAS</v>
       </c>
       <c r="D10" s="77" t="str">
-        <f>FI_Process!F14</f>
+        <f>FI_Process!F15</f>
         <v>Power Plant - Natural Gas</v>
       </c>
       <c r="E10" s="77" t="str">
@@ -4771,14 +4860,14 @@
         <v>52.56</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="18"/>
       <c r="C11" s="79" t="str">
-        <f>FI_Process!E15</f>
+        <f>FI_Process!E16</f>
         <v>EX_PP_WIND</v>
       </c>
       <c r="D11" s="80" t="str">
-        <f>FI_Process!F15</f>
+        <f>FI_Process!F16</f>
         <v>Power Plant - Wind Tuebine</v>
       </c>
       <c r="E11" s="80" t="str">
@@ -4809,51 +4898,92 @@
       <c r="O11" s="51"/>
       <c r="P11" s="51"/>
     </row>
-    <row r="12" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="21"/>
-      <c r="O12" s="58">
+    <row r="12" spans="2:16" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="18"/>
+      <c r="C12" s="117" t="str">
+        <f>FI_Process!E8</f>
+        <v>STG_DN_1P</v>
+      </c>
+      <c r="D12" s="117" t="str">
+        <f>FI_Process!F8</f>
+        <v>Storage</v>
+      </c>
+      <c r="E12" s="117" t="str">
+        <f>FI_Comm!E14</f>
+        <v>ELE_MV</v>
+      </c>
+      <c r="F12" s="117" t="str">
+        <f>E12</f>
+        <v>ELE_MV</v>
+      </c>
+      <c r="G12" s="117">
+        <f>I12/1</f>
+        <v>0.8</v>
+      </c>
+      <c r="H12" s="117">
+        <v>1</v>
+      </c>
+      <c r="I12" s="117">
+        <v>0.8</v>
+      </c>
+      <c r="J12" s="117">
+        <v>1</v>
+      </c>
+      <c r="K12" s="117">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L12" s="117">
+        <v>3</v>
+      </c>
+      <c r="M12" s="23"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+    </row>
+    <row r="13" spans="2:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="21"/>
+      <c r="O13" s="58">
         <f>SUM(O9:O10)</f>
         <v>132.45120000000003</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" s="9" t="s">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C18" s="9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="3:3" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
+    <row r="20" spans="3:3" ht="42" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C22" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="3:3" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="3:3" ht="42" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4864,15 +4994,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF049C56-8571-476E-80B4-2A2AA175E0B0}">
   <dimension ref="B2:K7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="90" t="s">
         <v>41</v>
       </c>
@@ -4886,7 +5016,7 @@
       <c r="J2" s="90"/>
       <c r="K2" s="90"/>
     </row>
-    <row r="3" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="55" t="s">
         <v>22</v>
       </c>
@@ -4918,7 +5048,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="91" t="s">
         <v>43</v>
       </c>
@@ -4950,7 +5080,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="85" t="s">
         <v>50</v>
       </c>
@@ -4976,13 +5106,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="89" t="str">
-        <f>FI_Process!E17</f>
+        <f>FI_Process!E18</f>
         <v>EX_ELC_GRID</v>
       </c>
       <c r="C6" s="89" t="str">
-        <f>FI_Process!F17</f>
+        <f>FI_Process!F18</f>
         <v>Existing Grid</v>
       </c>
       <c r="D6" s="89" t="str">
@@ -5004,7 +5134,7 @@
       <c r="J6" s="89"/>
       <c r="K6" s="89"/>
     </row>
-    <row r="7" spans="2:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:11" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5014,39 +5144,39 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8DE65A-CDBE-4BD0-8253-87A191EAA74A}">
   <dimension ref="B1:L25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="3.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="3.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>117</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="6"/>
     </row>
-    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="17"/>
       <c r="C4" s="46"/>
       <c r="D4" s="47"/>
       <c r="E4" s="48"/>
       <c r="F4" s="22"/>
     </row>
-    <row r="5" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="18"/>
       <c r="C5" s="56" t="s">
         <v>41</v>
@@ -5055,7 +5185,7 @@
       <c r="E5" s="38"/>
       <c r="F5" s="70"/>
     </row>
-    <row r="6" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18"/>
       <c r="C6" s="54" t="s">
         <v>2</v>
@@ -5070,7 +5200,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="18"/>
       <c r="C7" s="71" t="s">
         <v>119</v>
@@ -5083,7 +5213,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="18"/>
       <c r="C8" s="74" t="s">
         <v>50</v>
@@ -5094,7 +5224,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="18"/>
       <c r="C9" s="44" t="str">
         <f>FI_Comm!E$13</f>
@@ -5109,7 +5239,7 @@
         <v>113.63636363636364</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="18"/>
       <c r="C10" s="64" t="str">
         <f>FI_Comm!E$13</f>
@@ -5129,7 +5259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="18"/>
       <c r="C11" s="44" t="str">
         <f>FI_Comm!E$13</f>
@@ -5149,7 +5279,7 @@
         <v>5.6818181818181825</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="18"/>
       <c r="C12" s="64" t="str">
         <f>FI_Comm!E$13</f>
@@ -5169,7 +5299,7 @@
         <v>11.363636363636365</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="18"/>
       <c r="C13" s="44" t="str">
         <f>FI_Comm!E$13</f>
@@ -5189,7 +5319,7 @@
         <v>17.045454545454547</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="18"/>
       <c r="C14" s="64" t="str">
         <f>FI_Comm!E$13</f>
@@ -5209,7 +5339,7 @@
         <v>22.72727272727273</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="18"/>
       <c r="C15" s="44" t="str">
         <f>FI_Comm!E$13</f>
@@ -5229,7 +5359,7 @@
         <v>17.045454545454547</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="18"/>
       <c r="C16" s="64" t="str">
         <f>FI_Comm!E$13</f>
@@ -5249,7 +5379,7 @@
         <v>22.72727272727273</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="18"/>
       <c r="C17" s="79" t="str">
         <f>FI_Comm!E$13</f>
@@ -5273,15 +5403,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="19"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
       <c r="F18" s="21"/>
     </row>
-    <row r="20" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C21" s="36"/>
       <c r="D21" s="37"/>
       <c r="E21" s="37"/>
@@ -5295,7 +5425,7 @@
       <c r="K21" s="37"/>
       <c r="L21" s="38"/>
     </row>
-    <row r="22" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C22" s="40" t="s">
         <v>22</v>
       </c>
@@ -5327,7 +5457,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="42" x14ac:dyDescent="0.2">
       <c r="C23" s="42" t="s">
         <v>43</v>
       </c>
@@ -5359,7 +5489,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C24" s="49" t="s">
         <v>50</v>
       </c>
@@ -5385,13 +5515,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C25" s="66" t="str">
-        <f>FI_Process!E19</f>
+        <f>FI_Process!E20</f>
         <v>DMD_FIN_ELC</v>
       </c>
       <c r="D25" s="66" t="str">
-        <f>FI_Process!F19</f>
+        <f>FI_Process!F20</f>
         <v>Final electricity demand</v>
       </c>
       <c r="E25" s="66" t="str">
@@ -5420,12 +5550,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="154c1c0f-2c06-4f37-a5b1-faba3524bf7f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0be4b9af-ad17-4489-a21e-b8b210aeb5f9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5624,20 +5756,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="154c1c0f-2c06-4f37-a5b1-faba3524bf7f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0be4b9af-ad17-4489-a21e-b8b210aeb5f9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D6FCCB-655D-4190-91C8-88E3630C153E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{485776A6-5B40-46C5-9899-357C034833E4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="154c1c0f-2c06-4f37-a5b1-faba3524bf7f"/>
+    <ds:schemaRef ds:uri="0be4b9af-ad17-4489-a21e-b8b210aeb5f9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5662,12 +5795,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{485776A6-5B40-46C5-9899-357C034833E4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D6FCCB-655D-4190-91C8-88E3630C153E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="154c1c0f-2c06-4f37-a5b1-faba3524bf7f"/>
-    <ds:schemaRef ds:uri="0be4b9af-ad17-4489-a21e-b8b210aeb5f9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/VT_ELAND_ALL_V02.xlsx
+++ b/VT_ELAND_ALL_V02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/GalaLorenzo/Downloads/ELAND-main 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/GalaLorenzo/Documents/INNOENERGY/AGH/VEDA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C121F63B-FC07-314C-8F40-EC89262A9DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C9D806-F1A3-9D4F-A4FE-77361BF80A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15760" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="10" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Power Plants" sheetId="8" r:id="rId7"/>
     <sheet name="GRID" sheetId="13" r:id="rId8"/>
     <sheet name="Demand" sheetId="9" r:id="rId9"/>
+    <sheet name="TFM_Comm" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -563,6 +564,40 @@
         </r>
       </text>
     </comment>
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{CB7B22B4-418C-0D48-90A9-4E135BEEB15A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">With this symbol </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="238"/>
+          </rPr>
+          <t>\I:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>, this column is ignored from VEDA.
+It is just useful for your information</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -612,7 +647,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="223">
   <si>
     <t>Define Commodities</t>
   </si>
@@ -1218,6 +1253,69 @@
   </si>
   <si>
     <t>Electricity Medium Voltage</t>
+  </si>
+  <si>
+    <t>PEAK</t>
+  </si>
+  <si>
+    <t>Peak EQ Factor</t>
+  </si>
+  <si>
+    <t>ELE_EX_WIND_ON</t>
+  </si>
+  <si>
+    <t>WIND-ON</t>
+  </si>
+  <si>
+    <t>ELE_EX_PV</t>
+  </si>
+  <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>SOLAR</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>\|:</t>
+  </si>
+  <si>
+    <t>COM_PKRSV</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Timeslice</t>
+  </si>
+  <si>
+    <t>\|:Attribute</t>
+  </si>
+  <si>
+    <t>Value in Region</t>
+  </si>
+  <si>
+    <t>COM_PKFLX</t>
+  </si>
+  <si>
+    <t>1R1MOH01</t>
+  </si>
+  <si>
+    <t>2020, 2021</t>
+  </si>
+  <si>
+    <t>1R1MOH02</t>
+  </si>
+  <si>
+    <t>1R1MOH03</t>
+  </si>
+  <si>
+    <t>1R1MOH04</t>
   </si>
 </sst>
 </file>
@@ -1886,7 +1984,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2101,7 +2199,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3472,6 +3569,159 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A9A7A11-6A1E-8B4B-A40B-732407C9E2F4}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="71" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="67">
+        <v>0.18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="39" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="D10" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28" x14ac:dyDescent="0.2">
+      <c r="A11" s="71" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="71" t="s">
+        <v>213</v>
+      </c>
+      <c r="D11" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="71" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E12">
+        <v>8.2480999999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D13" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13">
+        <v>8.7642999999999999E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>219</v>
+      </c>
+      <c r="D14" t="s">
+        <v>221</v>
+      </c>
+      <c r="E14">
+        <v>8.7522000000000003E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>217</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>219</v>
+      </c>
+      <c r="D15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E15">
+        <v>0.102677</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA14610B-F5EC-4107-A8FB-0F277B7332F9}">
   <dimension ref="B2"/>
@@ -3500,7 +3750,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:L24"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -3763,110 +4013,156 @@
     </row>
     <row r="14" spans="2:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B14" s="18"/>
-      <c r="C14" s="118" t="s">
+      <c r="C14" s="77" t="s">
         <v>157</v>
       </c>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118" t="s">
+      <c r="D14" s="77"/>
+      <c r="E14" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="F14" s="118" t="s">
+      <c r="F14" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="G14" s="118" t="s">
+      <c r="G14" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="118"/>
-      <c r="I14" s="118" t="s">
+      <c r="H14" s="77"/>
+      <c r="I14" s="77" t="s">
         <v>187</v>
       </c>
-      <c r="J14" s="118"/>
-      <c r="K14" s="118"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
       <c r="L14" s="23"/>
     </row>
-    <row r="15" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="19"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="21"/>
-    </row>
-    <row r="18" spans="3:5" ht="19" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="105" t="s">
+    <row r="15" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="18"/>
+      <c r="C15" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77" t="s">
+        <v>205</v>
+      </c>
+      <c r="F15" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="G15" s="77" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77" t="s">
+        <v>187</v>
+      </c>
+      <c r="J15" s="77"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="23"/>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="18"/>
+      <c r="C16" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77" t="s">
+        <v>208</v>
+      </c>
+      <c r="F16" s="77" t="s">
+        <v>207</v>
+      </c>
+      <c r="G16" s="77" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77" t="s">
+        <v>187</v>
+      </c>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="23"/>
+    </row>
+    <row r="17" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="21"/>
+    </row>
+    <row r="20" spans="2:12" ht="19" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="105" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="105"/>
-      <c r="E18" s="105"/>
-    </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C19" s="62" t="s">
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C21" s="62" t="s">
         <v>140</v>
       </c>
-      <c r="D19" s="106" t="s">
+      <c r="D21" s="106" t="s">
         <v>141</v>
       </c>
-      <c r="E19" s="107"/>
-    </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C20" s="59" t="s">
+      <c r="E21" s="107"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C22" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="110" t="s">
+      <c r="D22" s="110" t="s">
         <v>139</v>
       </c>
-      <c r="E20" s="110"/>
-    </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C21" s="60" t="s">
+      <c r="E22" s="110"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C23" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="D21" s="109" t="s">
+      <c r="D23" s="109" t="s">
         <v>142</v>
       </c>
-      <c r="E21" s="109"/>
-    </row>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C22" s="59" t="s">
+      <c r="E23" s="109"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C24" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="D22" s="110" t="s">
+      <c r="D24" s="110" t="s">
         <v>143</v>
       </c>
-      <c r="E22" s="110"/>
-    </row>
-    <row r="23" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C23" s="60" t="s">
+      <c r="E24" s="110"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C25" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="D23" s="109" t="s">
+      <c r="D25" s="109" t="s">
         <v>146</v>
       </c>
-      <c r="E23" s="109"/>
-    </row>
-    <row r="24" spans="3:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="61" t="s">
+      <c r="E25" s="109"/>
+    </row>
+    <row r="26" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="D24" s="108" t="s">
+      <c r="D26" s="108" t="s">
         <v>147</v>
       </c>
-      <c r="E24" s="108"/>
+      <c r="E26" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D25:E25"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D20:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -3875,7 +4171,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D37998-97B2-47BE-BFC8-510092DE769F}">
-  <dimension ref="B2:L34"/>
+  <dimension ref="B2:L37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -4195,209 +4491,284 @@
     </row>
     <row r="17" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="18"/>
-      <c r="C17" s="87" t="s">
-        <v>178</v>
-      </c>
-      <c r="D17" s="87"/>
-      <c r="E17" s="87"/>
-      <c r="F17" s="87"/>
-      <c r="G17" s="87"/>
-      <c r="H17" s="87"/>
-      <c r="I17" s="87"/>
-      <c r="J17" s="87"/>
-      <c r="K17" s="87"/>
+      <c r="C17" s="117" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="117" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" s="117" t="s">
+        <v>204</v>
+      </c>
+      <c r="F17" s="117" t="s">
+        <v>177</v>
+      </c>
+      <c r="G17" s="117" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="117" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="117" t="s">
+        <v>187</v>
+      </c>
+      <c r="J17" s="117"/>
+      <c r="K17" s="117"/>
       <c r="L17" s="23"/>
     </row>
     <row r="18" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="18"/>
-      <c r="C18" s="68" t="s">
-        <v>183</v>
-      </c>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68" t="s">
-        <v>184</v>
-      </c>
-      <c r="F18" s="68" t="s">
-        <v>185</v>
-      </c>
-      <c r="G18" s="68" t="s">
+      <c r="C18" s="117" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117" t="s">
+        <v>206</v>
+      </c>
+      <c r="F18" s="117" t="s">
+        <v>207</v>
+      </c>
+      <c r="G18" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="H18" s="68" t="s">
+      <c r="H18" s="117" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="68" t="s">
+      <c r="I18" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
       <c r="L18" s="23"/>
     </row>
     <row r="19" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="18"/>
-      <c r="C19" s="85" t="s">
+      <c r="C19" s="87" t="s">
         <v>178</v>
       </c>
-      <c r="D19" s="85" t="s">
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="23"/>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="18"/>
+      <c r="C20" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="F20" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="G20" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="23"/>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="18"/>
+      <c r="C21" s="85" t="s">
+        <v>178</v>
+      </c>
+      <c r="D21" s="85" t="s">
         <v>179</v>
       </c>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="85"/>
-      <c r="J19" s="85"/>
-      <c r="K19" s="85"/>
-      <c r="L19" s="23"/>
-    </row>
-    <row r="20" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="18"/>
-      <c r="C20" s="89" t="s">
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="85"/>
+      <c r="J21" s="85"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="23"/>
+    </row>
+    <row r="22" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="18"/>
+      <c r="C22" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89" t="s">
+      <c r="D22" s="89"/>
+      <c r="E22" s="89" t="s">
         <v>181</v>
       </c>
-      <c r="F20" s="89" t="s">
+      <c r="F22" s="89" t="s">
         <v>182</v>
       </c>
-      <c r="G20" s="89" t="s">
+      <c r="G22" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="89" t="s">
+      <c r="H22" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="I20" s="89" t="s">
+      <c r="I22" s="89" t="s">
         <v>187</v>
       </c>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="23"/>
-    </row>
-    <row r="21" spans="2:12" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="19"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="21"/>
-    </row>
-    <row r="24" spans="2:12" ht="19" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="105" t="s">
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="23"/>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="18"/>
+      <c r="C23" s="117" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="117" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" s="117" t="s">
+        <v>204</v>
+      </c>
+      <c r="F23" s="117" t="s">
+        <v>177</v>
+      </c>
+      <c r="G23" s="117" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="117"/>
+      <c r="L23" s="23"/>
+    </row>
+    <row r="24" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="19"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="21"/>
+    </row>
+    <row r="27" spans="2:12" ht="19" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="105" t="s">
         <v>166</v>
       </c>
-      <c r="D24" s="105"/>
-      <c r="E24" s="105"/>
-    </row>
-    <row r="25" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C25" s="16" t="s">
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+    </row>
+    <row r="28" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C28" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="D25" s="112" t="s">
+      <c r="D28" s="112" t="s">
         <v>141</v>
       </c>
-      <c r="E25" s="113"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C26" s="63" t="s">
+      <c r="E28" s="113"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C29" s="63" t="s">
         <v>148</v>
       </c>
-      <c r="D26" s="116" t="s">
+      <c r="D29" s="116" t="s">
         <v>164</v>
       </c>
-      <c r="E26" s="116"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C27" s="60" t="s">
+      <c r="E29" s="116"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C30" s="60" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="114" t="s">
+      <c r="D30" s="114" t="s">
         <v>162</v>
       </c>
-      <c r="E27" s="114"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C28" s="59" t="s">
+      <c r="E30" s="114"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C31" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="D28" s="115" t="s">
+      <c r="D31" s="115" t="s">
         <v>160</v>
       </c>
-      <c r="E28" s="115"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C29" s="60" t="s">
+      <c r="E31" s="115"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C32" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="D29" s="114" t="s">
+      <c r="D32" s="114" t="s">
         <v>159</v>
       </c>
-      <c r="E29" s="114"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C30" s="59" t="s">
+      <c r="E32" s="114"/>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C33" s="59" t="s">
         <v>150</v>
       </c>
-      <c r="D30" s="115" t="s">
+      <c r="D33" s="115" t="s">
         <v>158</v>
       </c>
-      <c r="E30" s="115"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C31" s="60" t="s">
+      <c r="E33" s="115"/>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C34" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="D31" s="114" t="s">
+      <c r="D34" s="114" t="s">
         <v>165</v>
       </c>
-      <c r="E31" s="114"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C32" s="59" t="s">
+      <c r="E34" s="114"/>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C35" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="D32" s="115" t="s">
+      <c r="D35" s="115" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="115"/>
-    </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C33" s="60" t="s">
+      <c r="E35" s="115"/>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C36" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="D33" s="114" t="s">
+      <c r="D36" s="114" t="s">
         <v>156</v>
       </c>
-      <c r="E33" s="114"/>
-    </row>
-    <row r="34" spans="3:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="61" t="s">
+      <c r="E36" s="114"/>
+    </row>
+    <row r="37" spans="3:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="D34" s="111" t="s">
+      <c r="D37" s="111" t="s">
         <v>163</v>
       </c>
-      <c r="E34" s="111"/>
+      <c r="E37" s="111"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D35:E35"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="D25:E25"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D26:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -4562,20 +4933,20 @@
     </row>
     <row r="12" spans="2:8" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B12" s="18"/>
-      <c r="C12" s="117" t="str">
+      <c r="C12" s="68" t="str">
         <f>FI_Process!E8</f>
         <v>STG_DN_1P</v>
       </c>
-      <c r="D12" s="117" t="str">
+      <c r="D12" s="68" t="str">
         <f>FI_Process!F8</f>
         <v>Storage</v>
       </c>
-      <c r="E12" s="117" t="str">
+      <c r="E12" s="68" t="str">
         <f>FI_Comm!E14</f>
         <v>ELE_MV</v>
       </c>
-      <c r="F12" s="117"/>
-      <c r="G12" s="117"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
       <c r="H12" s="23"/>
     </row>
     <row r="13" spans="2:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4900,39 +5271,39 @@
     </row>
     <row r="12" spans="2:16" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B12" s="18"/>
-      <c r="C12" s="117" t="str">
+      <c r="C12" s="68" t="str">
         <f>FI_Process!E8</f>
         <v>STG_DN_1P</v>
       </c>
-      <c r="D12" s="117" t="str">
+      <c r="D12" s="68" t="str">
         <f>FI_Process!F8</f>
         <v>Storage</v>
       </c>
-      <c r="E12" s="117" t="str">
+      <c r="E12" s="68" t="str">
         <f>FI_Comm!E14</f>
         <v>ELE_MV</v>
       </c>
-      <c r="F12" s="117" t="str">
+      <c r="F12" s="68" t="str">
         <f>E12</f>
         <v>ELE_MV</v>
       </c>
-      <c r="G12" s="117">
+      <c r="G12" s="68">
         <f>I12/1</f>
         <v>0.8</v>
       </c>
-      <c r="H12" s="117">
+      <c r="H12" s="68">
         <v>1</v>
       </c>
-      <c r="I12" s="117">
+      <c r="I12" s="68">
         <v>0.8</v>
       </c>
-      <c r="J12" s="117">
+      <c r="J12" s="68">
         <v>1</v>
       </c>
-      <c r="K12" s="117">
+      <c r="K12" s="68">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="L12" s="117">
+      <c r="L12" s="68">
         <v>3</v>
       </c>
       <c r="M12" s="23"/>
@@ -4993,16 +5364,16 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF049C56-8571-476E-80B4-2A2AA175E0B0}">
-  <dimension ref="B2:K7"/>
+  <dimension ref="B2:L15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="18.1640625" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" customWidth="1"/>
+    <col min="7" max="8" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="90" t="s">
         <v>41</v>
       </c>
@@ -5015,8 +5386,9 @@
       <c r="I2" s="90"/>
       <c r="J2" s="90"/>
       <c r="K2" s="90"/>
-    </row>
-    <row r="3" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L2" s="90"/>
+    </row>
+    <row r="3" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="55" t="s">
         <v>22</v>
       </c>
@@ -5035,20 +5407,21 @@
       <c r="G3" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="H3" s="55" t="s">
+      <c r="H3" s="55"/>
+      <c r="I3" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="J3" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="55" t="s">
+      <c r="K3" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="K3" s="55" t="s">
+      <c r="L3" s="55" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" s="91" t="s">
         <v>43</v>
       </c>
@@ -5067,20 +5440,21 @@
       <c r="G4" s="91" t="s">
         <v>111</v>
       </c>
-      <c r="H4" s="91" t="s">
+      <c r="H4" s="91"/>
+      <c r="I4" s="91" t="s">
         <v>112</v>
       </c>
-      <c r="I4" s="91" t="s">
+      <c r="J4" s="91" t="s">
         <v>113</v>
       </c>
-      <c r="J4" s="91" t="s">
+      <c r="K4" s="91" t="s">
         <v>114</v>
       </c>
-      <c r="K4" s="91" t="s">
+      <c r="L4" s="91" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="85" t="s">
         <v>50</v>
       </c>
@@ -5093,26 +5467,27 @@
       <c r="G5" s="85" t="s">
         <v>131</v>
       </c>
-      <c r="H5" s="85" t="s">
-        <v>122</v>
-      </c>
+      <c r="H5" s="85"/>
       <c r="I5" s="85" t="s">
         <v>122</v>
       </c>
       <c r="J5" s="85" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="K5" s="85" t="s">
+      <c r="L5" s="85" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="89" t="str">
-        <f>FI_Process!E18</f>
+        <f>FI_Process!E20</f>
         <v>EX_ELC_GRID</v>
       </c>
       <c r="C6" s="89" t="str">
-        <f>FI_Process!F18</f>
+        <f>FI_Process!F20</f>
         <v>Existing Grid</v>
       </c>
       <c r="D6" s="89" t="str">
@@ -5127,14 +5502,204 @@
       <c r="G6" s="89">
         <v>1</v>
       </c>
-      <c r="H6" s="89">
+      <c r="H6" s="89"/>
+      <c r="I6" s="89">
         <v>0.88</v>
       </c>
-      <c r="I6" s="89"/>
       <c r="J6" s="89"/>
       <c r="K6" s="89"/>
-    </row>
-    <row r="7" spans="2:11" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
+      <c r="L6" s="89"/>
+    </row>
+    <row r="7" spans="2:12" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="90" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="90"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="90"/>
+      <c r="J9" s="90"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="90"/>
+    </row>
+    <row r="10" spans="2:12" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="I10" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="J10" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="K10" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="55" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="91" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="91" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="91" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="91" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="91" t="s">
+        <v>111</v>
+      </c>
+      <c r="H11" s="91" t="s">
+        <v>203</v>
+      </c>
+      <c r="I11" s="91" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="91" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" s="91" t="s">
+        <v>114</v>
+      </c>
+      <c r="L11" s="91" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="85" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="85" t="s">
+        <v>122</v>
+      </c>
+      <c r="K12" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="L12" s="85" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="89" t="str">
+        <f>FI_Process!E17</f>
+        <v>ELE_EX_WIND_ON</v>
+      </c>
+      <c r="C13" s="89" t="str">
+        <f>FI_Process!F17</f>
+        <v>Wind Onshore</v>
+      </c>
+      <c r="D13" s="89" t="str">
+        <f>FI_Comm!E15</f>
+        <v>WIND-ON</v>
+      </c>
+      <c r="E13" s="89" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="89">
+        <v>6.2279999999999998</v>
+      </c>
+      <c r="G13" s="89">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="H13" s="89">
+        <v>0.33</v>
+      </c>
+      <c r="I13" s="89">
+        <v>1</v>
+      </c>
+      <c r="J13" s="89">
+        <v>0.3</v>
+      </c>
+      <c r="K13" s="89">
+        <v>0</v>
+      </c>
+      <c r="L13" s="89">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="89" t="str">
+        <f>FI_Process!E18</f>
+        <v>ELE_EX_PV</v>
+      </c>
+      <c r="C14" s="89" t="str">
+        <f>FI_Process!F18</f>
+        <v>PV</v>
+      </c>
+      <c r="D14" s="89" t="str">
+        <f>FI_Comm!E16</f>
+        <v>SOLAR</v>
+      </c>
+      <c r="E14" s="117" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="117">
+        <v>3.9550000000000001</v>
+      </c>
+      <c r="G14" s="117">
+        <v>31.536000000000001</v>
+      </c>
+      <c r="H14" s="117">
+        <v>0.05</v>
+      </c>
+      <c r="I14" s="117">
+        <v>1</v>
+      </c>
+      <c r="J14" s="117">
+        <v>1</v>
+      </c>
+      <c r="K14" s="117">
+        <v>0</v>
+      </c>
+      <c r="L14" s="117">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5235,7 +5800,7 @@
       </c>
       <c r="E9" s="68"/>
       <c r="F9" s="45">
-        <f>100/GRID!H6</f>
+        <f>100/GRID!I6</f>
         <v>113.63636363636364</v>
       </c>
     </row>
@@ -5517,11 +6082,11 @@
     </row>
     <row r="25" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C25" s="66" t="str">
-        <f>FI_Process!E20</f>
+        <f>FI_Process!E22</f>
         <v>DMD_FIN_ELC</v>
       </c>
       <c r="D25" s="66" t="str">
-        <f>FI_Process!F20</f>
+        <f>FI_Process!F22</f>
         <v>Final electricity demand</v>
       </c>
       <c r="E25" s="66" t="str">
@@ -5561,6 +6126,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100765A2D8ABDD1064B8560F0E0020228D7" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="faba48c57225b8cf4893994d76bae982">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="154c1c0f-2c06-4f37-a5b1-faba3524bf7f" xmlns:ns3="0be4b9af-ad17-4489-a21e-b8b210aeb5f9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="653a6a65a0f1497e1436c43ea8aacb76" ns2:_="" ns3:_="">
     <xsd:import namespace="154c1c0f-2c06-4f37-a5b1-faba3524bf7f"/>
@@ -5755,15 +6329,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{485776A6-5B40-46C5-9899-357C034833E4}">
   <ds:schemaRefs>
@@ -5776,6 +6341,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D6FCCB-655D-4190-91C8-88E3630C153E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C2D764-5B27-4522-8FEB-F224FDBA4CB6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5792,12 +6365,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D6FCCB-655D-4190-91C8-88E3630C153E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>